--- a/registration_forms/033_media_access_registration_form--registration_forms.xlsx
+++ b/registration_forms/033_media_access_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1206,8 +1206,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'photo',_'label':_'photo'}</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'photo', 'label': 'Photo'}</t>
+          <t>Photo</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'video',_'label':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'video', 'label': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'interview',_'label':_'interview'}</t>
+          <t>interview</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'interview', 'label': 'Interview'}</t>
+          <t>Interview</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'all',_'label':_'all'}</t>
+          <t>all</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'all', 'label': 'All'}</t>
+          <t>All</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'journalist',_'label':_'journalist'}</t>
+          <t>journalist</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'journalist', 'label': 'Journalist'}</t>
+          <t>Journalist</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'camera_person',_'label':_'camera_person'}</t>
+          <t>camera_person</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'camera_person', 'label': 'Camera Person'}</t>
+          <t>Camera Person</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'photographer',_'label':_'photographer'}</t>
+          <t>photographer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'photographer', 'label': 'Photographer'}</t>
+          <t>Photographer</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_none,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': None, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_none,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': None, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'conference',_'label':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'conference', 'label': 'Conference'}</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'seminar',_'label':_'seminar'}</t>
+          <t>seminar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'seminar', 'label': 'Seminar'}</t>
+          <t>Seminar</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'workshop',_'label':_'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'workshop', 'label': 'Workshop'}</t>
+          <t>Workshop</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
